--- a/baseline_hepaus_pars.xlsx
+++ b/baseline_hepaus_pars.xlsx
@@ -540,76 +540,76 @@
         <v>25</v>
       </c>
       <c r="B2">
-        <v>17.35018532827379</v>
+        <v>18.48417578649617</v>
       </c>
       <c r="C2">
-        <v>308.1625472254378</v>
+        <v>336.6093924101857</v>
       </c>
       <c r="D2">
-        <v>379.702063421468</v>
+        <v>362.6634693098511</v>
       </c>
       <c r="E2">
-        <v>17.81217735045846</v>
+        <v>19.51076314459439</v>
       </c>
       <c r="F2">
-        <v>293.9405821174268</v>
+        <v>334.373192306528</v>
       </c>
       <c r="G2">
-        <v>384.4022276754265</v>
+        <v>375.4590379768111</v>
       </c>
       <c r="H2">
-        <v>21.24526949598164</v>
+        <v>21.86579141979038</v>
       </c>
       <c r="I2">
-        <v>90.42180651768149</v>
+        <v>101.9467323267382</v>
       </c>
       <c r="J2">
-        <v>688.1715947024986</v>
+        <v>709.3782833634586</v>
       </c>
       <c r="K2">
-        <v>21.40691555068578</v>
+        <v>24.87729082341614</v>
       </c>
       <c r="L2">
-        <v>89.4655047679428</v>
+        <v>104.2095467127555</v>
       </c>
       <c r="M2">
-        <v>689.6491914107214</v>
+        <v>739.1165571425611</v>
       </c>
       <c r="N2">
-        <v>1.20543568206766</v>
+        <v>1.246137635074309</v>
       </c>
       <c r="O2">
-        <v>2.142456006707206</v>
+        <v>2.391584698141559</v>
       </c>
       <c r="P2">
-        <v>9.096141078721722</v>
+        <v>6.982498587646266</v>
       </c>
       <c r="Q2">
-        <v>1.20543568206766</v>
+        <v>1.246137635074309</v>
       </c>
       <c r="R2">
-        <v>1.99862551720854</v>
+        <v>2.246608773545434</v>
       </c>
       <c r="S2">
-        <v>8.992539040527834</v>
+        <v>7.008045735217956</v>
       </c>
       <c r="T2">
-        <v>0.6151393162958267</v>
+        <v>0.6170378583123783</v>
       </c>
       <c r="U2">
-        <v>0.6786997806346581</v>
+        <v>0.6881388067942998</v>
       </c>
       <c r="V2">
-        <v>0.9562125838918474</v>
+        <v>1.068426268265968</v>
       </c>
       <c r="W2">
-        <v>0.6151393162958267</v>
+        <v>0.6167506274594454</v>
       </c>
       <c r="X2">
-        <v>0.6124018349142032</v>
+        <v>0.6210989077072122</v>
       </c>
       <c r="Y2">
-        <v>0.9374721360948978</v>
+        <v>1.02951459833655</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -617,76 +617,76 @@
         <v>26</v>
       </c>
       <c r="B3">
-        <v>0.05491685137255099</v>
+        <v>0.0529089448780045</v>
       </c>
       <c r="C3">
-        <v>0.01978299735190353</v>
+        <v>0.01972089867094264</v>
       </c>
       <c r="D3">
-        <v>0.01891828336329808</v>
+        <v>0.01915586180581189</v>
       </c>
       <c r="E3">
-        <v>0.05369126234472001</v>
+        <v>0.05109198959676253</v>
       </c>
       <c r="F3">
-        <v>0.02056094604294263</v>
+        <v>0.02032383817648103</v>
       </c>
       <c r="G3">
-        <v>0.01892821395888496</v>
+        <v>0.0191811790910337</v>
       </c>
       <c r="H3">
-        <v>0.05429699378345434</v>
+        <v>0.05337702947432052</v>
       </c>
       <c r="I3">
-        <v>0.0224663946525725</v>
+        <v>0.02204566892543731</v>
       </c>
       <c r="J3">
-        <v>0.01889594420981888</v>
+        <v>0.01888665172255115</v>
       </c>
       <c r="K3">
-        <v>0.05369665224983282</v>
+        <v>0.04913473409093153</v>
       </c>
       <c r="L3">
-        <v>0.02268632464744934</v>
+        <v>0.02215946038287137</v>
       </c>
       <c r="M3">
-        <v>0.01889548993635298</v>
+        <v>0.01887216237367744</v>
       </c>
       <c r="N3">
-        <v>0.101889274834068</v>
+        <v>0.09804766534194742</v>
       </c>
       <c r="O3">
-        <v>0.04944613164409468</v>
+        <v>0.04558949978006736</v>
       </c>
       <c r="P3">
-        <v>0.02428746796940192</v>
+        <v>0.02626313639551821</v>
       </c>
       <c r="Q3">
-        <v>0.101889274834068</v>
+        <v>0.09804766534194742</v>
       </c>
       <c r="R3">
-        <v>0.05045569840354656</v>
+        <v>0.04640989286416679</v>
       </c>
       <c r="S3">
-        <v>0.024352482228769</v>
+        <v>0.02621573227731289</v>
       </c>
       <c r="T3">
-        <v>0.1138601273686702</v>
+        <v>0.1099217914334042</v>
       </c>
       <c r="U3">
-        <v>0.05895904124852858</v>
+        <v>0.05494639158149636</v>
       </c>
       <c r="V3">
-        <v>0.02891227687330087</v>
+        <v>0.02678790885682546</v>
       </c>
       <c r="W3">
-        <v>0.1138601273686702</v>
+        <v>0.1105047786779234</v>
       </c>
       <c r="X3">
-        <v>0.06047695208639974</v>
+        <v>0.05626047406919778</v>
       </c>
       <c r="Y3">
-        <v>0.02895081790571305</v>
+        <v>0.02706801197766756</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -694,76 +694,76 @@
         <v>27</v>
       </c>
       <c r="B4">
-        <v>0.1020575942901578</v>
+        <v>0.1011781992762632</v>
       </c>
       <c r="C4">
-        <v>0.08785935974388812</v>
+        <v>0.08776298942508712</v>
       </c>
       <c r="D4">
-        <v>0.08759091970802883</v>
+        <v>0.08762134026202249</v>
       </c>
       <c r="E4">
-        <v>0.1017301197815588</v>
+        <v>0.1004907922041731</v>
       </c>
       <c r="F4">
-        <v>0.08189311357013153</v>
+        <v>0.08238622317077363</v>
       </c>
       <c r="G4">
-        <v>0.08896000246192073</v>
+        <v>0.09164525107179181</v>
       </c>
       <c r="H4">
-        <v>0.1805177308707649</v>
+        <v>0.1794567298441801</v>
       </c>
       <c r="I4">
-        <v>0.1522719736514048</v>
+        <v>0.1510013014757943</v>
       </c>
       <c r="J4">
-        <v>0.1424614793486583</v>
+        <v>0.1424198304073822</v>
       </c>
       <c r="K4">
-        <v>0.180359394807826</v>
+        <v>0.175150532538964</v>
       </c>
       <c r="L4">
-        <v>0.1487314679085107</v>
+        <v>0.1475988791882794</v>
       </c>
       <c r="M4">
-        <v>0.1428510392473332</v>
+        <v>0.1427223039092161</v>
       </c>
       <c r="N4">
-        <v>0.1600283688213251</v>
+        <v>0.1554790947547423</v>
       </c>
       <c r="O4">
-        <v>0.1138801724592838</v>
+        <v>0.1079863817025137</v>
       </c>
       <c r="P4">
-        <v>0.07542363225861722</v>
+        <v>0.0786967327387546</v>
       </c>
       <c r="Q4">
-        <v>0.1600283688213251</v>
+        <v>0.1554790947547423</v>
       </c>
       <c r="R4">
-        <v>0.1098547308431051</v>
+        <v>0.1047540835716057</v>
       </c>
       <c r="S4">
-        <v>0.07615299335188513</v>
+        <v>0.07941749656960151</v>
       </c>
       <c r="T4">
-        <v>0.1642009778836675</v>
+        <v>0.1594645402372321</v>
       </c>
       <c r="U4">
-        <v>0.1171815983784434</v>
+        <v>0.1111013229628084</v>
       </c>
       <c r="V4">
-        <v>0.07276340183460943</v>
+        <v>0.06945360897488909</v>
       </c>
       <c r="W4">
-        <v>0.1642009778836675</v>
+        <v>0.1601728829226593</v>
       </c>
       <c r="X4">
-        <v>0.1103770209003428</v>
+        <v>0.1055125191633786</v>
       </c>
       <c r="Y4">
-        <v>0.07366634479915002</v>
+        <v>0.07060066431412124</v>
       </c>
     </row>
   </sheetData>

--- a/baseline_hepaus_pars.xlsx
+++ b/baseline_hepaus_pars.xlsx
@@ -540,76 +540,76 @@
         <v>25</v>
       </c>
       <c r="B2">
-        <v>18.48417578649617</v>
+        <v>0.001874215221225689</v>
       </c>
       <c r="C2">
-        <v>336.6093924101857</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>362.6634693098511</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>19.51076314459439</v>
+        <v>0.006498029333137876</v>
       </c>
       <c r="F2">
-        <v>334.373192306528</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>375.4590379768111</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>21.86579141979038</v>
+        <v>0.07201714046726834</v>
       </c>
       <c r="I2">
-        <v>101.9467323267382</v>
+        <v>0.08053147861785559</v>
       </c>
       <c r="J2">
-        <v>709.3782833634586</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>24.87729082341614</v>
+        <v>0.07281075646015447</v>
       </c>
       <c r="L2">
-        <v>104.2095467127555</v>
+        <v>0.06707195875772902</v>
       </c>
       <c r="M2">
-        <v>739.1165571425611</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>1.246137635074309</v>
+        <v>0.01764947577338688</v>
       </c>
       <c r="O2">
-        <v>2.391584698141559</v>
+        <v>0.1057305648110574</v>
       </c>
       <c r="P2">
-        <v>6.982498587646266</v>
+        <v>0.05110793889513847</v>
       </c>
       <c r="Q2">
-        <v>1.246137635074309</v>
+        <v>0.01539884873066284</v>
       </c>
       <c r="R2">
-        <v>2.246608773545434</v>
+        <v>0.1122801476243039</v>
       </c>
       <c r="S2">
-        <v>7.008045735217956</v>
+        <v>0.05191839529364917</v>
       </c>
       <c r="T2">
-        <v>0.6170378583123783</v>
+        <v>0.01449149295716399</v>
       </c>
       <c r="U2">
-        <v>0.6881388067942998</v>
+        <v>0.1057584260281608</v>
       </c>
       <c r="V2">
-        <v>1.068426268265968</v>
+        <v>0.04933866385601611</v>
       </c>
       <c r="W2">
-        <v>0.6167506274594454</v>
+        <v>0.01574999784171747</v>
       </c>
       <c r="X2">
-        <v>0.6210989077072122</v>
+        <v>0.1125046710674354</v>
       </c>
       <c r="Y2">
-        <v>1.02951459833655</v>
+        <v>0.05060047430165641</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -617,76 +617,76 @@
         <v>26</v>
       </c>
       <c r="B3">
-        <v>0.0529089448780045</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.01972089867094264</v>
+        <v>0.001046554730485141</v>
       </c>
       <c r="D3">
-        <v>0.01915586180581189</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0.05109198959676253</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0.02032383817648103</v>
+        <v>0.003539141918654456</v>
       </c>
       <c r="G3">
-        <v>0.0191811790910337</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.05337702947432052</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.02204566892543731</v>
+        <v>0.04680863286045586</v>
       </c>
       <c r="J3">
-        <v>0.01888665172255115</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>0.04913473409093153</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>0.02215946038287137</v>
+        <v>0.04001662084563257</v>
       </c>
       <c r="M3">
-        <v>0.01887216237367744</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>0.09804766534194742</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>0.04558949978006736</v>
+        <v>0.07378192745720677</v>
       </c>
       <c r="P3">
-        <v>0.02626313639551821</v>
+        <v>0.02001156611786236</v>
       </c>
       <c r="Q3">
-        <v>0.09804766534194742</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>0.04640989286416679</v>
+        <v>0.0789068659064342</v>
       </c>
       <c r="S3">
-        <v>0.02621573227731289</v>
+        <v>0.02232450547449797</v>
       </c>
       <c r="T3">
-        <v>0.1099217914334042</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0.05494639158149636</v>
+        <v>0.07191197825374149</v>
       </c>
       <c r="V3">
-        <v>0.02678790885682546</v>
+        <v>0.01715729149576042</v>
       </c>
       <c r="W3">
-        <v>0.1105047786779234</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.05626047406919778</v>
+        <v>0.0771100016636177</v>
       </c>
       <c r="Y3">
-        <v>0.02706801197766756</v>
+        <v>0.01848407446277296</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -694,76 +694,76 @@
         <v>27</v>
       </c>
       <c r="B4">
-        <v>0.1011781992762632</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.08776298942508712</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0.08762134026202249</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0.1004907922041731</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0.08238622317077363</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>0.09164525107179181</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.1794567298441801</v>
+        <v>0.02856915313965698</v>
       </c>
       <c r="I4">
-        <v>0.1510013014757943</v>
+        <v>0.03354328833119392</v>
       </c>
       <c r="J4">
-        <v>0.1424198304073822</v>
+        <v>0.0001169917773218092</v>
       </c>
       <c r="K4">
-        <v>0.175150532538964</v>
+        <v>0.02889837061617884</v>
       </c>
       <c r="L4">
-        <v>0.1475988791882794</v>
+        <v>0.02725555195072539</v>
       </c>
       <c r="M4">
-        <v>0.1427223039092161</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>0.1554790947547423</v>
+        <v>0.008829069306242408</v>
       </c>
       <c r="O4">
-        <v>0.1079863817025137</v>
+        <v>0.04909522011805342</v>
       </c>
       <c r="P4">
-        <v>0.0786967327387546</v>
+        <v>0.0183114699703855</v>
       </c>
       <c r="Q4">
-        <v>0.1554790947547423</v>
+        <v>0.008223131141445511</v>
       </c>
       <c r="R4">
-        <v>0.1047540835716057</v>
+        <v>0.05319451351973938</v>
       </c>
       <c r="S4">
-        <v>0.07941749656960151</v>
+        <v>0.01916773438224637</v>
       </c>
       <c r="T4">
-        <v>0.1594645402372321</v>
+        <v>0.007488220337184709</v>
       </c>
       <c r="U4">
-        <v>0.1111013229628084</v>
+        <v>0.04917911062581767</v>
       </c>
       <c r="V4">
-        <v>0.06945360897488909</v>
+        <v>0.01706006061135295</v>
       </c>
       <c r="W4">
-        <v>0.1601728829226593</v>
+        <v>0.007946805154462298</v>
       </c>
       <c r="X4">
-        <v>0.1055125191633786</v>
+        <v>0.05310095774960328</v>
       </c>
       <c r="Y4">
-        <v>0.07060066431412124</v>
+        <v>0.01760178903955496</v>
       </c>
     </row>
   </sheetData>

--- a/baseline_hepaus_pars.xlsx
+++ b/baseline_hepaus_pars.xlsx
@@ -540,7 +540,7 @@
         <v>25</v>
       </c>
       <c r="B2">
-        <v>0.001874215221225689</v>
+        <v>0.007097718441662877</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.006498029333137876</v>
+        <v>0.01143691084226823</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -558,58 +558,58 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.07201714046726834</v>
+        <v>0.07114689544329814</v>
       </c>
       <c r="I2">
-        <v>0.08053147861785559</v>
+        <v>0.06971363991925919</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0.07281075646015447</v>
+        <v>0.07191721963239829</v>
       </c>
       <c r="L2">
-        <v>0.06707195875772902</v>
+        <v>0.06114455740975585</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.01764947577338688</v>
+        <v>0.02134527879576505</v>
       </c>
       <c r="O2">
-        <v>0.1057305648110574</v>
+        <v>0.1023298545001873</v>
       </c>
       <c r="P2">
-        <v>0.05110793889513847</v>
+        <v>0.0502333741107631</v>
       </c>
       <c r="Q2">
-        <v>0.01539884873066284</v>
+        <v>0.01498735944549001</v>
       </c>
       <c r="R2">
-        <v>0.1122801476243039</v>
+        <v>0.1080151387616798</v>
       </c>
       <c r="S2">
-        <v>0.05191839529364917</v>
+        <v>0.05119714733256019</v>
       </c>
       <c r="T2">
-        <v>0.01449149295716399</v>
+        <v>0.01414788774637125</v>
       </c>
       <c r="U2">
-        <v>0.1057584260281608</v>
+        <v>0.1035446928855022</v>
       </c>
       <c r="V2">
-        <v>0.04933866385601611</v>
+        <v>0.0481204486972803</v>
       </c>
       <c r="W2">
-        <v>0.01574999784171747</v>
+        <v>0.01566400698941073</v>
       </c>
       <c r="X2">
-        <v>0.1125046710674354</v>
+        <v>0.1060040330306262</v>
       </c>
       <c r="Y2">
-        <v>0.05060047430165641</v>
+        <v>0.04596523270822953</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.001046554730485141</v>
+        <v>0.002079649168390302</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.003539141918654456</v>
+        <v>0.006209636087092455</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.04680863286045586</v>
+        <v>0.03916885160069115</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -647,7 +647,7 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.04001662084563257</v>
+        <v>0.03785291949971936</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -656,37 +656,37 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <v>0.07378192745720677</v>
+        <v>0.07395263983162534</v>
       </c>
       <c r="P3">
-        <v>0.02001156611786236</v>
+        <v>0.01982389443142465</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>0.0789068659064342</v>
+        <v>0.07551095007802587</v>
       </c>
       <c r="S3">
-        <v>0.02232450547449797</v>
+        <v>0.02110554553901601</v>
       </c>
       <c r="T3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.07191197825374149</v>
+        <v>0.07021749256249879</v>
       </c>
       <c r="V3">
-        <v>0.01715729149576042</v>
+        <v>0.01678373457369408</v>
       </c>
       <c r="W3">
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.0771100016636177</v>
+        <v>0.07143430590943579</v>
       </c>
       <c r="Y3">
-        <v>0.01848407446277296</v>
+        <v>0.01784380019491508</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -694,7 +694,7 @@
         <v>27</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>0.0004684957907661966</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -703,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>0.002903780425430426</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -712,58 +712,58 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0.02856915313965698</v>
+        <v>0.02807451648682033</v>
       </c>
       <c r="I4">
-        <v>0.03354328833119392</v>
+        <v>0.028578324079253</v>
       </c>
       <c r="J4">
-        <v>0.0001169917773218092</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>0.02889837061617884</v>
+        <v>0.02847404560877372</v>
       </c>
       <c r="L4">
-        <v>0.02725555195072539</v>
+        <v>0.02498834258864928</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.008829069306242408</v>
+        <v>0.009388704143793775</v>
       </c>
       <c r="O4">
-        <v>0.04909522011805342</v>
+        <v>0.04756664643987916</v>
       </c>
       <c r="P4">
-        <v>0.0183114699703855</v>
+        <v>0.01796389667419278</v>
       </c>
       <c r="Q4">
-        <v>0.008223131141445511</v>
+        <v>0.008037133057887115</v>
       </c>
       <c r="R4">
-        <v>0.05319451351973938</v>
+        <v>0.05083666875773984</v>
       </c>
       <c r="S4">
-        <v>0.01916773438224637</v>
+        <v>0.01869083970390598</v>
       </c>
       <c r="T4">
-        <v>0.007488220337184709</v>
+        <v>0.007335859006049441</v>
       </c>
       <c r="U4">
-        <v>0.04917911062581767</v>
+        <v>0.0479799648176841</v>
       </c>
       <c r="V4">
-        <v>0.01706006061135295</v>
+        <v>0.01662834300444652</v>
       </c>
       <c r="W4">
-        <v>0.007946805154462298</v>
+        <v>0.007904392637386529</v>
       </c>
       <c r="X4">
-        <v>0.05310095774960328</v>
+        <v>0.04936630285788995</v>
       </c>
       <c r="Y4">
-        <v>0.01760178903955496</v>
+        <v>0.01627315155747025</v>
       </c>
     </row>
   </sheetData>

--- a/baseline_hepaus_pars.xlsx
+++ b/baseline_hepaus_pars.xlsx
@@ -540,7 +540,7 @@
         <v>25</v>
       </c>
       <c r="B2">
-        <v>0.007097718441662877</v>
+        <v>0.01051794769975141</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.01143691084226823</v>
+        <v>0.01507724755386264</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -558,58 +558,58 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.07114689544329814</v>
+        <v>0.04943484112528182</v>
       </c>
       <c r="I2">
-        <v>0.06971363991925919</v>
+        <v>0.05749354510602905</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0.07191721963239829</v>
+        <v>0.05091179793756886</v>
       </c>
       <c r="L2">
-        <v>0.06114455740975585</v>
+        <v>0.05155998707116184</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.02134527879576505</v>
+        <v>0.009608781640753402</v>
       </c>
       <c r="O2">
-        <v>0.1023298545001873</v>
+        <v>0.09628635515893874</v>
       </c>
       <c r="P2">
-        <v>0.0502333741107631</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.01498735944549001</v>
+        <v>0.01957063800053362</v>
       </c>
       <c r="R2">
-        <v>0.1080151387616798</v>
+        <v>0.09936377421759289</v>
       </c>
       <c r="S2">
-        <v>0.05119714733256019</v>
+        <v>0.02703077749752273</v>
       </c>
       <c r="T2">
-        <v>0.01414788774637125</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>0.1035446928855022</v>
+        <v>0.09295402397141127</v>
       </c>
       <c r="V2">
-        <v>0.0481204486972803</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>0.01566400698941073</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>0.1060040330306262</v>
+        <v>0.0962528982306496</v>
       </c>
       <c r="Y2">
-        <v>0.04596523270822953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -620,25 +620,25 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.002079649168390302</v>
+        <v>0.01056006334940322</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.002903493405796415</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.006209636087092455</v>
+        <v>0.01311497665879789</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.00570318881116943</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.03916885160069115</v>
+        <v>0.03196109488883473</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -647,46 +647,46 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.03785291949971936</v>
+        <v>0.03034334905459155</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>0.0001367386013686529</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
       <c r="O3">
-        <v>0.07395263983162534</v>
+        <v>0.07026833955168205</v>
       </c>
       <c r="P3">
-        <v>0.01982389443142465</v>
+        <v>0.006047389804599908</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>0.07551095007802587</v>
+        <v>0.07332072973109485</v>
       </c>
       <c r="S3">
-        <v>0.02110554553901601</v>
+        <v>0.01680398668767565</v>
       </c>
       <c r="T3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.07021749256249879</v>
+        <v>0.06059890756196004</v>
       </c>
       <c r="V3">
-        <v>0.01678373457369408</v>
+        <v>0.003369517557889813</v>
       </c>
       <c r="W3">
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.07143430590943579</v>
+        <v>0.06201198678473215</v>
       </c>
       <c r="Y3">
-        <v>0.01784380019491508</v>
+        <v>0.006059874523072448</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -694,76 +694,76 @@
         <v>27</v>
       </c>
       <c r="B4">
-        <v>0.0004684957907661966</v>
+        <v>0.002756864562100694</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>0.005118862498409795</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.001214885223922022</v>
       </c>
       <c r="E4">
-        <v>0.002903780425430426</v>
+        <v>0.005307612424099882</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>0.006045493799189486</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.004083107588420261</v>
       </c>
       <c r="H4">
-        <v>0.02807451648682033</v>
+        <v>0.01845595371260583</v>
       </c>
       <c r="I4">
-        <v>0.028578324079253</v>
+        <v>0.02302391989935904</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0.02847404560877372</v>
+        <v>0.0188134928976882</v>
       </c>
       <c r="L4">
-        <v>0.02498834258864928</v>
+        <v>0.0206336808280933</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.009388704143793775</v>
+        <v>0.005548911459377188</v>
       </c>
       <c r="O4">
-        <v>0.04756664643987916</v>
+        <v>0.04361486185639436</v>
       </c>
       <c r="P4">
-        <v>0.01796389667419278</v>
+        <v>0.005871222014536862</v>
       </c>
       <c r="Q4">
-        <v>0.008037133057887115</v>
+        <v>0.009367922961065086</v>
       </c>
       <c r="R4">
-        <v>0.05083666875773984</v>
+        <v>0.04545776499809355</v>
       </c>
       <c r="S4">
-        <v>0.01869083970390598</v>
+        <v>0.01266780699886743</v>
       </c>
       <c r="T4">
-        <v>0.007335859006049441</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>0.0479799648176841</v>
+        <v>0.04112668400665978</v>
       </c>
       <c r="V4">
-        <v>0.01662834300444652</v>
+        <v>0.001446813952219339</v>
       </c>
       <c r="W4">
-        <v>0.007904392637386529</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.04936630285788995</v>
+        <v>0.04296649555541652</v>
       </c>
       <c r="Y4">
-        <v>0.01627315155747025</v>
+        <v>0.004204543476530648</v>
       </c>
     </row>
   </sheetData>

--- a/baseline_hepaus_pars.xlsx
+++ b/baseline_hepaus_pars.xlsx
@@ -540,76 +540,76 @@
         <v>25</v>
       </c>
       <c r="B2">
-        <v>0.01051794769975141</v>
+        <v>0.03051318141494384</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>0.02796591702464171</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.02479003896658477</v>
       </c>
       <c r="E2">
-        <v>0.01507724755386264</v>
+        <v>0.03328968315928135</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.03118689317312339</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.02800094599310921</v>
       </c>
       <c r="H2">
-        <v>0.04943484112528182</v>
+        <v>0.05713198782585014</v>
       </c>
       <c r="I2">
-        <v>0.05749354510602905</v>
+        <v>0.08998773221936768</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.02025931150932803</v>
       </c>
       <c r="K2">
-        <v>0.05091179793756886</v>
+        <v>0.05822686489629961</v>
       </c>
       <c r="L2">
-        <v>0.05155998707116184</v>
+        <v>0.08165472686938281</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01747514693788067</v>
       </c>
       <c r="N2">
-        <v>0.009608781640753402</v>
+        <v>0.02941062792337431</v>
       </c>
       <c r="O2">
-        <v>0.09628635515893874</v>
+        <v>0.1430740074250123</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.03806280382888134</v>
       </c>
       <c r="Q2">
-        <v>0.01957063800053362</v>
+        <v>0.03469974214782147</v>
       </c>
       <c r="R2">
-        <v>0.09936377421759289</v>
+        <v>0.1470846084351365</v>
       </c>
       <c r="S2">
-        <v>0.02703077749752273</v>
+        <v>0.0611932101400479</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.02223921846267217</v>
       </c>
       <c r="U2">
-        <v>0.09295402397141127</v>
+        <v>0.1387358620224587</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.03366355723062085</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>0.0218440785285197</v>
       </c>
       <c r="X2">
-        <v>0.0962528982306496</v>
+        <v>0.1431617569721631</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>0.03703968641465211</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -620,73 +620,73 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.01056006334940322</v>
+        <v>0.01212849574271695</v>
       </c>
       <c r="D3">
-        <v>0.002903493405796415</v>
+        <v>0.003900374661836533</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.01311497665879789</v>
+        <v>0.01515430044480195</v>
       </c>
       <c r="G3">
-        <v>0.00570318881116943</v>
+        <v>0.006984768964831673</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.03196109488883473</v>
+        <v>0.03399474256567313</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.0004110362302523104</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.03034334905459155</v>
+        <v>0.03240832454731998</v>
       </c>
       <c r="M3">
-        <v>0.0001367386013686529</v>
+        <v>0.00159379624958803</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
       <c r="O3">
-        <v>0.07026833955168205</v>
+        <v>0.07482814432730167</v>
       </c>
       <c r="P3">
-        <v>0.006047389804599908</v>
+        <v>0.007166946369130384</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>0.07332072973109485</v>
+        <v>0.07811692544387486</v>
       </c>
       <c r="S3">
-        <v>0.01680398668767565</v>
+        <v>0.01836372180497686</v>
       </c>
       <c r="T3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.06059890756196004</v>
+        <v>0.06416829297742288</v>
       </c>
       <c r="V3">
-        <v>0.003369517557889813</v>
+        <v>0.004089884762585236</v>
       </c>
       <c r="W3">
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.06201198678473215</v>
+        <v>0.06562138228811359</v>
       </c>
       <c r="Y3">
-        <v>0.006059874523072448</v>
+        <v>0.006740434065088519</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -694,76 +694,76 @@
         <v>27</v>
       </c>
       <c r="B4">
-        <v>0.002756864562100694</v>
+        <v>0.007895383346397599</v>
       </c>
       <c r="C4">
-        <v>0.005118862498409795</v>
+        <v>0.006508335565186765</v>
       </c>
       <c r="D4">
-        <v>0.001214885223922022</v>
+        <v>0.004244858685274545</v>
       </c>
       <c r="E4">
-        <v>0.005307612424099882</v>
+        <v>0.008665196727542762</v>
       </c>
       <c r="F4">
-        <v>0.006045493799189486</v>
+        <v>0.007665659602711081</v>
       </c>
       <c r="G4">
-        <v>0.004083107588420261</v>
+        <v>0.005522188797230347</v>
       </c>
       <c r="H4">
-        <v>0.01845595371260583</v>
+        <v>0.01571405415116532</v>
       </c>
       <c r="I4">
-        <v>0.02302391989935904</v>
+        <v>0.0236591560007733</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.002480556101737041</v>
       </c>
       <c r="K4">
-        <v>0.0188134928976882</v>
+        <v>0.01605059855153084</v>
       </c>
       <c r="L4">
-        <v>0.0206336808280933</v>
+        <v>0.02134603911467514</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>0.002377136604830659</v>
       </c>
       <c r="N4">
-        <v>0.005548911459377188</v>
+        <v>0.007796614930550785</v>
       </c>
       <c r="O4">
-        <v>0.04361486185639436</v>
+        <v>0.04494004476350123</v>
       </c>
       <c r="P4">
-        <v>0.005871222014536862</v>
+        <v>0.007233072738217437</v>
       </c>
       <c r="Q4">
-        <v>0.009367922961065086</v>
+        <v>0.009291901652926097</v>
       </c>
       <c r="R4">
-        <v>0.04545776499809355</v>
+        <v>0.04680504577911453</v>
       </c>
       <c r="S4">
-        <v>0.01266780699886743</v>
+        <v>0.01393034441665536</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.005779860317440278</v>
       </c>
       <c r="U4">
-        <v>0.04112668400665978</v>
+        <v>0.04220735158686391</v>
       </c>
       <c r="V4">
-        <v>0.001446813952219339</v>
+        <v>0.005657074673653855</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>0.00566041859036996</v>
       </c>
       <c r="X4">
-        <v>0.04296649555541652</v>
+        <v>0.044041514070348</v>
       </c>
       <c r="Y4">
-        <v>0.004204543476530648</v>
+        <v>0.006872805198325699</v>
       </c>
     </row>
   </sheetData>

--- a/baseline_hepaus_pars.xlsx
+++ b/baseline_hepaus_pars.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>atsi_0-14_M</t>
   </si>
@@ -98,6 +98,9 @@
   </si>
   <si>
     <t>ltc_rate</t>
+  </si>
+  <si>
+    <t>hepb_pop</t>
   </si>
 </sst>
 </file>
@@ -455,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Y5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -540,76 +543,76 @@
         <v>25</v>
       </c>
       <c r="B2">
-        <v>0.03051318141494384</v>
+        <v>0.03089410213172191</v>
       </c>
       <c r="C2">
-        <v>0.02796591702464171</v>
+        <v>0.0305745562088925</v>
       </c>
       <c r="D2">
-        <v>0.02479003896658477</v>
+        <v>0.03056097516011015</v>
       </c>
       <c r="E2">
-        <v>0.03328968315928135</v>
+        <v>0.03372758073576571</v>
       </c>
       <c r="F2">
-        <v>0.03118689317312339</v>
+        <v>0.02945915292389633</v>
       </c>
       <c r="G2">
-        <v>0.02800094599310921</v>
+        <v>0.0308029979770892</v>
       </c>
       <c r="H2">
-        <v>0.05713198782585014</v>
+        <v>0.05722862951041827</v>
       </c>
       <c r="I2">
-        <v>0.08998773221936768</v>
+        <v>0.09722166518693395</v>
       </c>
       <c r="J2">
-        <v>0.02025931150932803</v>
+        <v>0.03162874447704608</v>
       </c>
       <c r="K2">
-        <v>0.05822686489629961</v>
+        <v>0.05830896392722033</v>
       </c>
       <c r="L2">
-        <v>0.08165472686938281</v>
+        <v>0.08801479042865616</v>
       </c>
       <c r="M2">
-        <v>0.01747514693788067</v>
+        <v>0.02928285852391169</v>
       </c>
       <c r="N2">
-        <v>0.02941062792337431</v>
+        <v>0.03409746954550255</v>
       </c>
       <c r="O2">
-        <v>0.1430740074250123</v>
+        <v>0.1340865400114631</v>
       </c>
       <c r="P2">
-        <v>0.03806280382888134</v>
+        <v>0.04313016447496309</v>
       </c>
       <c r="Q2">
-        <v>0.03469974214782147</v>
+        <v>0.04198140427556354</v>
       </c>
       <c r="R2">
-        <v>0.1470846084351365</v>
+        <v>0.1372644245406097</v>
       </c>
       <c r="S2">
-        <v>0.0611932101400479</v>
+        <v>0.06268087038119591</v>
       </c>
       <c r="T2">
-        <v>0.02223921846267217</v>
+        <v>0.02285938408551424</v>
       </c>
       <c r="U2">
-        <v>0.1387358620224587</v>
+        <v>0.1357427379795318</v>
       </c>
       <c r="V2">
-        <v>0.03366355723062085</v>
+        <v>0.0401446830337178</v>
       </c>
       <c r="W2">
-        <v>0.0218440785285197</v>
+        <v>0.02197601458325275</v>
       </c>
       <c r="X2">
-        <v>0.1431617569721631</v>
+        <v>0.1411662486248771</v>
       </c>
       <c r="Y2">
-        <v>0.03703968641465211</v>
+        <v>0.04357228609129225</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -620,73 +623,73 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.01212849574271695</v>
+        <v>0.3439124267108704</v>
       </c>
       <c r="D3">
-        <v>0.003900374661836533</v>
+        <v>0.3279239843153031</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.01515430044480195</v>
+        <v>0.4433252877148028</v>
       </c>
       <c r="G3">
-        <v>0.006984768964831673</v>
+        <v>0.3991300004074109</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.03399474256567313</v>
+        <v>0.1942460515940013</v>
       </c>
       <c r="J3">
-        <v>0.0004110362302523104</v>
+        <v>0.1225181194632424</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.03240832454731998</v>
+        <v>0.2317153804074366</v>
       </c>
       <c r="M3">
-        <v>0.00159379624958803</v>
+        <v>0.1535812428981457</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
       <c r="O3">
-        <v>0.07482814432730167</v>
+        <v>0.3703135523506091</v>
       </c>
       <c r="P3">
-        <v>0.007166946369130384</v>
+        <v>0.2148403451673404</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>0.07811692544387486</v>
+        <v>0.3867673176916075</v>
       </c>
       <c r="S3">
-        <v>0.01836372180497686</v>
+        <v>0.2512701054329264</v>
       </c>
       <c r="T3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.06416829297742288</v>
+        <v>0.2778070734004207</v>
       </c>
       <c r="V3">
-        <v>0.004089884762585236</v>
+        <v>0.1379504983633199</v>
       </c>
       <c r="W3">
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.06562138228811359</v>
+        <v>0.2796595448676114</v>
       </c>
       <c r="Y3">
-        <v>0.006740434065088519</v>
+        <v>0.1392764976623408</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -694,76 +697,153 @@
         <v>27</v>
       </c>
       <c r="B4">
-        <v>0.007895383346397599</v>
+        <v>0.008019965953786925</v>
       </c>
       <c r="C4">
-        <v>0.006508335565186765</v>
+        <v>0.0121834206640053</v>
       </c>
       <c r="D4">
-        <v>0.004244858685274545</v>
+        <v>0.007424151904896087</v>
       </c>
       <c r="E4">
-        <v>0.008665196727542762</v>
+        <v>0.00880897903149149</v>
       </c>
       <c r="F4">
-        <v>0.007665659602711081</v>
+        <v>0.01229271134807236</v>
       </c>
       <c r="G4">
-        <v>0.005522188797230347</v>
+        <v>0.01071207849804358</v>
       </c>
       <c r="H4">
-        <v>0.01571405415116532</v>
+        <v>0.01578814771344233</v>
       </c>
       <c r="I4">
-        <v>0.0236591560007733</v>
+        <v>0.02895837881743451</v>
       </c>
       <c r="J4">
-        <v>0.002480556101737041</v>
+        <v>0.009771503541742619</v>
       </c>
       <c r="K4">
-        <v>0.01605059855153084</v>
+        <v>0.01612106893238667</v>
       </c>
       <c r="L4">
-        <v>0.02134603911467514</v>
+        <v>0.02720953328093583</v>
       </c>
       <c r="M4">
-        <v>0.002377136604830659</v>
+        <v>0.01067496700795744</v>
       </c>
       <c r="N4">
-        <v>0.007796614930550785</v>
+        <v>0.009127574126286491</v>
       </c>
       <c r="O4">
-        <v>0.04494004476350123</v>
+        <v>0.04688574115292207</v>
       </c>
       <c r="P4">
-        <v>0.007233072738217437</v>
+        <v>0.01405155765386609</v>
       </c>
       <c r="Q4">
-        <v>0.009291901652926097</v>
+        <v>0.01141091822183344</v>
       </c>
       <c r="R4">
-        <v>0.04680504577911453</v>
+        <v>0.04854281512108397</v>
       </c>
       <c r="S4">
-        <v>0.01393034441665536</v>
+        <v>0.0197496823106496</v>
       </c>
       <c r="T4">
-        <v>0.005779860317440278</v>
+        <v>0.005962366433440293</v>
       </c>
       <c r="U4">
-        <v>0.04220735158686391</v>
+        <v>0.04527512352812219</v>
       </c>
       <c r="V4">
-        <v>0.005657074673653855</v>
+        <v>0.01205697921698358</v>
       </c>
       <c r="W4">
-        <v>0.00566041859036996</v>
+        <v>0.00571097526797895</v>
       </c>
       <c r="X4">
-        <v>0.044041514070348</v>
+        <v>0.04765658255559675</v>
       </c>
       <c r="Y4">
-        <v>0.006872805198325699</v>
+        <v>0.01338069908873494</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5">
+        <v>341.3039116833738</v>
+      </c>
+      <c r="C5">
+        <v>3846.705852325087</v>
+      </c>
+      <c r="D5">
+        <v>422.430052430877</v>
+      </c>
+      <c r="E5">
+        <v>292.1368801944367</v>
+      </c>
+      <c r="F5">
+        <v>3395.905963155159</v>
+      </c>
+      <c r="G5">
+        <v>456.4802338322769</v>
+      </c>
+      <c r="H5">
+        <v>554.9237931976769</v>
+      </c>
+      <c r="I5">
+        <v>18122.93767656985</v>
+      </c>
+      <c r="J5">
+        <v>4813.807411767233</v>
+      </c>
+      <c r="K5">
+        <v>520.954206580923</v>
+      </c>
+      <c r="L5">
+        <v>13452.26608593391</v>
+      </c>
+      <c r="M5">
+        <v>4419.627994170854</v>
+      </c>
+      <c r="N5">
+        <v>542.4549302270934</v>
+      </c>
+      <c r="O5">
+        <v>8049.080070679094</v>
+      </c>
+      <c r="P5">
+        <v>2031.850814213146</v>
+      </c>
+      <c r="Q5">
+        <v>321.2026299516812</v>
+      </c>
+      <c r="R5">
+        <v>5566.74228479948</v>
+      </c>
+      <c r="S5">
+        <v>1608.986472851946</v>
+      </c>
+      <c r="T5">
+        <v>3943.355934863285</v>
+      </c>
+      <c r="U5">
+        <v>68207.90425225932</v>
+      </c>
+      <c r="V5">
+        <v>19197.61925310961</v>
+      </c>
+      <c r="W5">
+        <v>2262.955811736267</v>
+      </c>
+      <c r="X5">
+        <v>47234.80759080181</v>
+      </c>
+      <c r="Y5">
+        <v>14415.87304865684</v>
       </c>
     </row>
   </sheetData>
